--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.69847277439114</v>
+        <v>9.051001825838561</v>
       </c>
       <c r="D2" t="n">
-        <v>56.18502921013066</v>
+        <v>9.130067246646233</v>
       </c>
       <c r="E2" t="n">
-        <v>17.76404442953796</v>
+        <v>2.886657219799918</v>
       </c>
       <c r="F2" t="n">
-        <v>17.30058529946729</v>
+        <v>2.811345111163435</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.06207931295499</v>
+        <v>7.647587888355186</v>
       </c>
       <c r="D3" t="n">
-        <v>43.40609243103783</v>
+        <v>7.053490020043649</v>
       </c>
       <c r="E3" t="n">
-        <v>17.76404442953796</v>
+        <v>2.886657219799918</v>
       </c>
       <c r="F3" t="n">
-        <v>17.30058529946729</v>
+        <v>2.811345111163435</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.44675108043484</v>
+        <v>2.347597050570662</v>
       </c>
       <c r="D4" t="n">
-        <v>14.80384446134276</v>
+        <v>2.405624724968199</v>
       </c>
       <c r="E4" t="n">
-        <v>17.76404442953796</v>
+        <v>2.886657219799918</v>
       </c>
       <c r="F4" t="n">
-        <v>17.30058529946729</v>
+        <v>2.811345111163435</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
